--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cfd_010/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cfd_010/extracted.xlsx
@@ -490,6 +490,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -655,11 +660,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G4" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -826,6 +826,46 @@
       </text>
     </comment>
     <comment ref="I8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="G9" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="I9" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1473,12 +1513,12 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Unsteady CFD to rank candidate stent geometries and confirm selected design hemodynamic acceptability prior to tool-up</t>
+          <t>Unsteady CFD model to rank stent geometries by near-wall shear environment and confirm Pattern B hemodynamic acceptability prior to tool-up</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>An unsteady incompressible Navier–Stokes CFD model of Pattern B cobalt-chromium drug-eluting coronary stent deployed in a 3.0 mm mildly curved coronary phantom. The model predicts TAWSS and OSI fields to rank three candidate lattice patterns and to verify that the selected design's hemodynamic footprint falls within ranges measured in an independent phantom PIV experiment under matched pulsatile flow conditions.</t>
+          <t>An unsteady incompressible Navier–Stokes CFD model (Ansys Fluent 2024 R1) is used to compare three candidate cobalt-chromium drug-eluting coronary stent patterns (A, B, C) under pulsatile flow in a micro-CT-based phantom geometry. For the selected Pattern B, predicted TAWSS and OSI fields must fall within pre-specified tolerance of independent PIV phantom measurements. Results drive design-freeze decisions; bench, animal, and clinical testing remain downstream gatekeepers.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1516,9 +1556,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md — "Credibility Report — CFD of Coronary Stent Hemodynamics to Support Design Freeze," Fluids Group CardioDesign R&amp;D, 2026-08-05</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2114,7 +2154,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Hemodynamic Acceptability Requirement</t>
+          <t>Hemodynamic Acceptability Requirement for Pattern B</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -2124,7 +2164,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Predicted OSI95 and TAWSS distribution for Pattern B must fall within the envelope measured in the anatomically matched phantom PIV experiment under matched flow conditions; velocity nRMSE ≤10% (peak)/≤12% (mean), pressure drop within 7%, TAWSS/OSI Pearson r ≥ 0.85, median difference &lt; 15%, KS p &gt; 0.1; design ranking differences must exceed combined numerical and input uncertainties</t>
+          <t>Predicted TAWSS and OSI95 distributions for Pattern B must agree with independent PIV phantom measurements within pre-specified tolerances (velocity nRMSE ≤ 10%/12%, pressure drop within 7%, TAWSS/OSI spatial Pearson r ≥ 0.85, median difference &lt; 15%, KS p &gt; 0.1); design ranking must be stable relative to combined uncertainties</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2146,13 +2186,13 @@
       </c>
       <c r="B4" s="41" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2024 R1 Unsteady CFD Model — Coronary Stent Pattern B</t>
+          <t>Unsteady Incompressible CFD Model — Coronary Stent Pattern B</t>
         </is>
       </c>
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Incompressible unsteady Navier–Stokes laminar CFD model of Pattern B stent in 3.0 mm curved phantom; 6.0M polyhedral cells, second-order spatial and temporal discretization, pulsatile inlet from measured pump trace, rigid walls, Newtonian glycerol-water surrogate for bench runs</t>
+          <t>Ansys Fluent 2024 R1 incompressible laminar Navier–Stokes model of stent-deployed 3.0 mm coronary phantom; polyhedral mesh 6.0M cells; second-order spatial/temporal discretization; micro-CT-based geometry; pulsatile inlet waveform from Transonic TS410</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2166,13 +2206,13 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>FlowLab LLC TR-PIV Experimental Dataset FL-2026-042</t>
+          <t>FlowLab LLC TR-PIV Phantom Dataset</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Time-resolved PIV phase-averaged velocity fields (40 phase bins, 500 fps) acquired in silicone phantom with refractive-index-matched glycerol-water surrogate by independent laboratory FlowLab LLC; velocity uncertainty ±3%, near-wall shear proxy uncertainty 10–12%</t>
+          <t>Time-resolved PIV velocity fields in silicone phantom under matched pulsatile flow; 40 phase-averaged bins; velocity uncertainty ±3%; near-wall shear proxy uncertainty ~10–12%; acquired independently by FlowLab LLC</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2186,13 +2226,13 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>Micro-CT Geometry Dataset — Pattern B Deployed Phantom</t>
+          <t>Micro-CT Phantom Geometry Dataset</t>
         </is>
       </c>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Micro-CT scan at 10 μm voxel size of Pattern B stent deployed in silicone phantom; segmented in Mimics 26.0; 95th-percentile surface deviation from raw point cloud 8 μm, maximum 22 μm</t>
+          <t>10 μm voxel micro-CT scan of deployed Stent B in silicone phantom; segmented in Mimics 26.0; 95th percentile surface deviation 8 μm, max 22 μm versus raw point cloud</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
@@ -2206,13 +2246,13 @@
       </c>
       <c r="B7" s="41" t="inlineStr">
         <is>
-          <t>Fluid Rheology Measurements — Anton Paar MCR 302</t>
+          <t>Fluid Property Measurements</t>
         </is>
       </c>
       <c r="C7" s="24" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>Oscillatory rheometer measurements of 40% glycerol-water surrogate density and viscosity at 37°C; uncertainty ±0.5% for μ and ±0.2% for ρ; Carreau–Yasuda parameters verified against published rheograms for in vivo what-if runs</t>
+          <t>Density and viscosity of 40% glycerol-water surrogate measured by Anton Paar MCR 302 oscillatory rheometer at 37°C; uncertainty ±0.5% (μ), ±0.2% (ρ); Carreau–Yasuda parameters verified against published rheograms for in vivo what-if runs</t>
         </is>
       </c>
       <c r="E7" s="33" t="n"/>
@@ -2354,7 +2394,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Velocity Field Comparison — CFD vs. TR-PIV</t>
+          <t>Poiseuille Flow Code Verification</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -2369,12 +2409,12 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Normalized RMS difference in velocity profiles at 10 cross-sections compared between CFD (Pattern B, medium mesh, Δt=1.0 ms) and phase-averaged TR-PIV fields at peak and mean flow phases</t>
+          <t>Fully developed laminar flow in a 3D circular pipe solved on 50k-cell mesh; parabolic velocity profile recovered</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>FlowLab LLC TR-PIV dataset FL-2026-042</t>
+          <t>Analytical Poiseuille solution</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
@@ -2384,12 +2424,12 @@
       </c>
       <c r="G3" s="39" t="inlineStr">
         <is>
-          <t>PIV correlation peak ratio uncertainty (±3% velocity); CFD combined uncertainty ~8–10% RSS for TAWSS</t>
+          <t>Grid refinement with observed order of convergence</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>nRMSE 7.1% (peak flow), 9.3% (mean flow); bias −1.8% vs PIV; both within pre-specified targets of ≤10% and ≤12%</t>
+          <t>L2 norm error &lt; 0.2%; observed order 1.98 (expected 2.0)</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
@@ -2401,7 +2441,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Pressure Drop Comparison — CFD vs. Validyne DP45 Transducers</t>
+          <t>Lid-Driven Cavity Benchmark</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2412,27 +2452,23 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Pressure drop across the stented segment predicted by CFD compared against transducer measurements in the phantom experiment</t>
+          <t>3D lid-driven cavity at Re=1000 simulated on 1.2M polyhedral cells; centerline velocity profiles compared to literature benchmark</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>Validyne DP45 differential pressure transducer measurements</t>
+          <t>Published benchmark data (literature)</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G4" s="41" t="inlineStr">
-        <is>
-          <t>Acceptance target ±7%; measurement uncertainty from calibrated transducers</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" s="33" t="n"/>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>CFD 3.2% higher than measured; within pre-specified ±7% target</t>
+          <t>Deviation &lt; 2.5%; grid refinement trend converges toward benchmark values</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2444,7 +2480,7 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>TAWSS Spatial Map Comparison — CFD vs. PIV-Derived</t>
+          <t>Mesh and Time-Step Convergence Study</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -2455,12 +2491,12 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Spatial correlation and distributional comparison of time-averaged wall shear stress maps between CFD prediction and PIV-derived near-wall extrapolations over the stented segment</t>
+          <t>Three-level mesh refinement (2.1M, 6.0M, 14.8M cells) and three-level time-step study (2.0, 1.0, 0.5 ms); GCI and Richardson extrapolation applied to pressure drop, TAWSS, and OSI95</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>PIV-derived TAWSS maps from FL-2026-042</t>
+          <t>Richardson extrapolation / Grid Convergence Index framework</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
@@ -2470,12 +2506,12 @@
       </c>
       <c r="G5" s="41" t="inlineStr">
         <is>
-          <t>Pearson r, Kolmogorov–Smirnov test, median difference; PIV near-wall gradient uncertainty 10–12%</t>
+          <t>GCI (factor of safety 1.25) and Richardson extrapolation</t>
         </is>
       </c>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>Pearson r = 0.89; median difference −6.4%; KS p = 0.21; hotspot co-location 93% within 0.2 mm</t>
+          <t>Fine-grid GCI for TAWSS 3.8%; medium-grid GCI 6.9%; OSI95 mesh variation 4.5%; time-step variation 2.1%; pressure drop Richardson bias 2.6% on medium mesh; observed order ~1.9</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -2487,7 +2523,7 @@
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>OSI Spatial Map Comparison — CFD vs. PIV-Derived</t>
+          <t>PIV Velocity Field Comparison</t>
         </is>
       </c>
       <c r="B6" s="41" t="inlineStr">
@@ -2498,12 +2534,12 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Spatial correlation and distributional comparison of oscillatory shear index maps between CFD and PIV-derived values</t>
+          <t>CFD velocity profiles at 10 cross-sections compared to TR-PIV phase-averaged fields at peak and mean flow conditions</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>PIV-derived OSI maps from FL-2026-042</t>
+          <t>FlowLab LLC TR-PIV dataset (FL-2026-042)</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
@@ -2513,12 +2549,12 @@
       </c>
       <c r="G6" s="41" t="inlineStr">
         <is>
-          <t>Pearson r, Kolmogorov–Smirnov test, median difference</t>
+          <t>nRMSE; PIV velocity uncertainty ±3% propagated through comparison</t>
         </is>
       </c>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>Pearson r = 0.86; median difference +4.9%; KS p = 0.18</t>
+          <t>nRMSE 7.1% at peak flow (target ≤ 10%); nRMSE 9.3% at mean flow (target ≤ 12%); bias −1.8%</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2530,7 +2566,7 @@
     <row r="7" ht="15" customHeight="1" s="18">
       <c r="A7" s="41" t="inlineStr">
         <is>
-          <t>Mesh and Time-Step Refinement Study</t>
+          <t>Pressure Drop Comparison</t>
         </is>
       </c>
       <c r="B7" s="41" t="inlineStr">
@@ -2541,12 +2577,12 @@
       <c r="C7" s="33" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>Three-level mesh refinement (2.1M, 6.0M, 14.8M cells) and three-level time-step study (Δt = 2.0, 1.0, 0.5 ms) to quantify discretization error in pressure drop, TAWSS, and OSI95</t>
+          <t>CFD-predicted pressure drop across stented segment compared to Validyne DP45 differential pressure transducer measurements</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr">
         <is>
-          <t>Richardson extrapolation and GCI analysis</t>
+          <t>Validyne DP45 transducer measurements</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
@@ -2556,12 +2592,12 @@
       </c>
       <c r="G7" s="41" t="inlineStr">
         <is>
-          <t>Grid Convergence Index (GCI, factor of safety 1.25), Richardson extrapolation, observed-order calculation</t>
+          <t>Direct percentage difference relative to measured value</t>
         </is>
       </c>
       <c r="H7" s="41" t="inlineStr">
         <is>
-          <t>TAWSS GCI fine grid 3.8%; medium grid GCI 6.9%; OSI95 mesh variation 4.5%; time-step variation 2.1%; pressure drop Richardson bias 2.6%; observed order ~1.9</t>
+          <t>CFD 3.2% higher than measured (target ≤ 7%)</t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
@@ -2573,7 +2609,7 @@
     <row r="8" ht="15" customHeight="1" s="18">
       <c r="A8" s="41" t="inlineStr">
         <is>
-          <t>Code Verification — Canonical Flow Tests</t>
+          <t>TAWSS and OSI Spatial Map Comparison</t>
         </is>
       </c>
       <c r="B8" s="41" t="inlineStr">
@@ -2584,12 +2620,12 @@
       <c r="C8" s="33" t="n"/>
       <c r="D8" s="41" t="inlineStr">
         <is>
-          <t>Verification of Ansys Fluent solver against analytical Poiseuille flow and lid-driven cavity benchmark prior to stent simulations</t>
+          <t>Spatial distribution of time-averaged wall shear stress (TAWSS) and oscillatory shear index (OSI) compared between CFD and PIV-derived maps; Pearson correlation, KS test, and median difference assessed</t>
         </is>
       </c>
       <c r="E8" s="41" t="inlineStr">
         <is>
-          <t>Analytical parabolic velocity profile (Poiseuille); published lid-driven cavity benchmark at Re=1000</t>
+          <t>FlowLab LLC TR-PIV derived wall shear indices (FL-2026-042)</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
@@ -2599,12 +2635,12 @@
       </c>
       <c r="G8" s="41" t="inlineStr">
         <is>
-          <t>L2 norm error, observed order of convergence, deviation percentage</t>
+          <t>Pearson r; Kolmogorov–Smirnov test; median difference; near-wall shear proxy uncertainty ~10–12%</t>
         </is>
       </c>
       <c r="H8" s="41" t="inlineStr">
         <is>
-          <t>Poiseuille L2 error &lt; 0.2%, observed order 1.98; lid-driven cavity centerline deviation &lt; 2.5%</t>
+          <t>TAWSS: r=0.89, median diff −6.4%, KS p=0.21; OSI: r=0.86, median diff +4.9%, KS p=0.18; hotspot co-location 93% within 0.2 mm</t>
         </is>
       </c>
       <c r="I8" s="42" t="inlineStr">
@@ -2614,14 +2650,47 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="18">
-      <c r="A9" s="24" t="n"/>
-      <c r="B9" s="24" t="n"/>
+      <c r="A9" s="41" t="inlineStr">
+        <is>
+          <t>Sensitivity and Uncertainty Budget Analysis</t>
+        </is>
+      </c>
+      <c r="B9" s="41" t="inlineStr">
+        <is>
+          <t>ValidationResult</t>
+        </is>
+      </c>
       <c r="C9" s="33" t="n"/>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="25" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="33" t="n"/>
-      <c r="H9" s="33" t="n"/>
+      <c r="D9" s="41" t="inlineStr">
+        <is>
+          <t>Parametric sensitivity study varying blood rheology model, inlet trace phase, stent positioning tolerances, and wall rigidity assumption; RSS combined uncertainty estimated for TAWSS area-average</t>
+        </is>
+      </c>
+      <c r="E9" s="41" t="inlineStr">
+        <is>
+          <t>Design-to-design differences (Pattern A vs. B ΔTAWSS = +12%)</t>
+        </is>
+      </c>
+      <c r="F9" s="41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G9" s="41" t="inlineStr">
+        <is>
+          <t>Root-sum-square combination of independent contributions; 1D elastic tube surrogate for wall compliance</t>
+        </is>
+      </c>
+      <c r="H9" s="41" t="inlineStr">
+        <is>
+          <t>Combined simulation-side uncertainty ~8–10% for TAWSS area-average; rheology effect −4.1% strut wakes; inlet phase ±1.5% OSI95; positioning ±4% local peak shear; wall rigidity &lt;5% near-wall shear modulation</t>
+        </is>
+      </c>
+      <c r="I9" s="42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="18">
       <c r="A10" s="24" t="n"/>
@@ -2818,12 +2887,12 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Commercial solver with documented QA; version-controlled case files; analyst qualifications documented</t>
+          <t>Commercial solver with documented quality processes; version-controlled case files; analyst qualifications demonstrated</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2024 R1 (commercial, double precision) used with documented solver build ID recorded in run log. All case/journal files tracked in Git LFS with SHA-256 hashes; mesh and data files archived to corporate vault tagged cd-stentB-v37. Python post-processing scripts have 88% pytest coverage and were validated on synthetic datasets. Analysts hold 6–12 years cardiovascular CFD experience with documented QA curriculum refresher (April 2026). Two-step peer review including cold-eye numerical review performed. Pre-departure/arrival checklists for each run. Bitwise-identical results confirmed on independent hardware node.</t>
+          <t>Ansys Fluent 2024 R1 (double precision) used — commercial solver with published theory guide and established QA processes. All case and journal files tracked in Git LFS with SHA-256 hashes; geometry, mesh, and solution files archived to corporate vault tagged cd-stentB-v37. Python post-processing scripts unit-tested with pytest (88% coverage) and validated on synthetic datasets. Run log records dates, hardware, solver build ID, and deviations. Peer review checklists attached. Lead analyst 12 years cardiovascular CFD experience; supporting analyst 6 years; both completed internal CFD QA curriculum (refreshed April 2026). Two-step review process including cold-eye aero-team review. Independent analysts (JD, ML) reproduced baseline run with outputs matching within 0.8%.</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2851,12 +2920,12 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Demonstration of correct equation solving against analytical or benchmark solutions with quantified convergence order</t>
+          <t>Comparison to analytical solutions or benchmarks demonstrating correct implementation of governing equations; convergence order consistent with numerical scheme</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Two canonical verification tests executed prior to stent cases: (1) 3D Poiseuille pipe flow recovered parabolic velocity with L2 error &lt; 0.2% on 50k-cell mesh and second-order convergence confirmed (observed order 1.98); (2) 3D lid-driven cavity at Re=1000 compared against published benchmark with deviation &lt; 2.5% on 1.2M polyhedral cells with expected convergence trend. Both confirm second-order spatial accuracy of the solver for laminar incompressible flow.</t>
+          <t>Two canonical verification problems executed: (1) Poiseuille flow in 3D circular pipe — L2 velocity error &lt; 0.2% on 50k-cell mesh, observed order 1.98 confirming second-order spatial accuracy; (2) 3D lid-driven cavity Re=1000 — centerline velocity deviation &lt; 2.5% vs. published benchmark on 1.2M polyhedral cells with convergent trend under refinement. Both tests directly demonstrate solver correctness and analyst competence for laminar incompressible flows. Hardware determinism confirmed: bitwise-identical results across two separate compute nodes.</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2880,16 +2949,16 @@
         <v>3</v>
       </c>
       <c r="D7" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Mesh and time-step convergence demonstrated with quantified GCI; residual discretization error small relative to design differences</t>
+          <t>Mesh convergence demonstrated quantitatively; GCI or equivalent error estimate provided for primary QoIs</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Three-level mesh refinement (2.1M, 6.0M, 14.8M cells) and three-level time-step study (2.0, 1.0, 0.5 ms) performed. GCI computed with factor of safety 1.25: TAWSS fine-grid GCI 3.8%, medium-grid GCI 6.9%. OSI95 mesh variation 4.5%, time-step variation 2.1%. Pressure drop Richardson bias 2.6% at peak flow. Observed spatial order ~1.9, consistent with second-order scheme. Periodicity confirmed (cycle-to-cycle WSS change &lt; 0.3%). Local hotspot peak shear changes &lt; 6% between medium and fine grids. Discretization errors are small relative to design-to-design differences (ΔTAWSS ~12%).</t>
+          <t>Three-level mesh refinement (2.1M coarse, 6.0M medium, 14.8M fine cells) with uniform refinement in strut-adjacent and recirculation zones. Three-level time-step study (2.0, 1.0, 0.5 ms). GCI computed with factor of safety 1.25: fine-grid GCI for TAWSS 3.8%, medium-grid GCI 6.9%. Richardson extrapolation gives 2.6% pressure drop bias on medium mesh. OSI95 mesh-induced variation 4.5%; time-step-induced variation 2.1%. Local hotspot peak WSS changes &lt; 6% between medium and fine; spatial location shifts &lt; 0.1 mm. Periodicity confirmed (cycle-to-cycle WSS change &lt; 0.3%). Detailed GCI plots in Appendix B. Production runs use medium mesh with fine-grid spot checks, with explicit justification.</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2917,12 +2986,12 @@
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Convergence criteria defined and met each time step; mass conservation demonstrated</t>
+          <t>Residual targets defined and met; mass conservation verified; monitor point convergence demonstrated</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Scaled residuals required below 1×10⁻⁶ each time step for all equations. Mass imbalance required below 0.1% per time step. Monitor points (bulk flow, pressure drop, area-averaged WSS) required steady to within 0.5% between time steps. All criteria documented in run log. Periodicity confirmed over last two of eight simulated cardiac cycles. Pressure–velocity coupling via coupled solver with pseudo-transient continuation. Solver convergence explicitly monitored and documented.</t>
+          <t>Scaled residuals required below 1×10⁻⁶ each time step for all equations. Mass imbalance monitored and maintained below 0.1% per time step. Monitor points for bulk flow, pressure drop, and area-averaged WSS confirmed steady to within 0.5% between time steps. Coupled pressure–velocity solver with pseudo-transient continuation used. Run log records solver convergence for each simulation. Bitwise-identical results across hardware nodes confirm deterministic solver behavior.</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2950,12 +3019,12 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Independent reproduction of results; boundary condition verification; mesh quality confirmation; peer review documented</t>
+          <t>Independent review of model setup; boundary condition verification; mesh quality checks documented</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>Independent analysts (JD and ML) reproduced baseline Pattern B run on the same mesh and BCs; key outputs matched within 0.8%. Pre-departure and arrival checklists verified units, BC alignment, and mesh quality metrics (skewness &lt; 0.85, aspect ratio &lt; 50 in prisms, orthogonality &gt; 0.2) for each run. Mesh quality histograms and y+ maps documented in Appendix A. Two-step peer review: midstream review after mesh/time studies and final sign-off with cold-eye review from independent aero team analyst. Inlet tracking error ≤1% RMS confirmed. Solver settings templated in version-controlled journal files to prevent inter-analyst drift.</t>
+          <t>Pre-departure and arrival checklists executed for each run covering units, BC alignment, and mesh quality metrics (skewness &lt; 0.85, aspect ratio &lt; 50 in prisms, orthogonality &gt; 0.2). Mesh quality histograms and y+ maps archived in Appendix A (y+ &lt; 0.8 everywhere). Inlet BC tracking error confirmed at 1% RMS versus measured pump trace. Outlet pressure tuned to match measured mean pressure drop (validated within 2%). Two independent analysts (JD, ML) reproduced baseline run within 0.8% on all QoIs. Two-step review process: midstream review after mesh/time studies and final cold-eye review by external aero-team analyst. Key settings templated in Git LFS to prevent drift between analysts.</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2979,16 +3048,16 @@
         <v>3</v>
       </c>
       <c r="D10" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Governing equations justified for flow regime; key assumptions documented and bounded; turbulence/rheology model selection rationale provided</t>
+          <t>Governing equation selection justified; key physical assumptions documented and bounded; sensitivity to model-form choices assessed</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>Incompressible Navier–Stokes with laminar solver justified by Re ≈ 350 (below laminar-turbulent threshold) and PIV spectra showing TKE &lt; 0.002 m²/s² with no broadband energy cascade. Laminar vs. SST k–ω comparison at peak flow showed TAWSS difference 5.6%, OSI95 difference 1.8%, with laminar model showing better agreement with PIV. Rigid-wall assumption bounded: 1D elastic tube model estimates &lt; 5% WSS modulation; supported by Morbiducci 2009 literature for Re &lt; 500. Newtonian assumption exact for bench glycerol-water fluid. Carreau–Yasuda model verified against published rheograms for in vivo what-if runs. Known limitations (patient-specific compliance, surface roughness, out-of-plane flows) explicitly documented in Section 14.</t>
+          <t>Incompressible laminar Navier–Stokes selected and justified: Re ≈ 350, below laminar-turbulent thresholds; PIV spectra confirm no broadband energy cascade (TKE &lt; 0.002 m²/s² everywhere). SST k–ω comparison at peak flow showed area-averaged TAWSS differs by only 5.6% and OSI95 by 1.8%, supporting laminar selection. Rigid-wall assumption bounded: 1D elastic tube estimate shows &lt;5% near-wall shear modulation for mid-LAD compliance; literature support cited (Morbiducci 2009). Isothermal assumption: temperature controlled to ±0.5°C in both CFD and PIV. Newtonian assumption exact for bench fluid; Carreau–Yasuda sensitivity for in vivo runs shows TAWSS shifts of −4.1% in strut wakes vs. design differences of 12%. Limitations (rigid walls, patient specificity, non-Newtonian low-shear zones) explicitly documented in Section 14.</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -3016,12 +3085,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Material properties from measurement with uncertainty; geometry from metrology with quantified deviation; inlet BC from measured waveform</t>
+          <t>Material properties from measurement with quantified uncertainty; geometry from metrology; boundary conditions from calibrated instruments</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>Fluid density and viscosity measured by oscillatory rheometer (Anton Paar MCR 302) with uncertainty ±0.5% (μ) and ±0.2% (ρ) at 37°C. Geometry from micro-CT at 10 μm voxel size; metrology comparison of triangulated surface to raw point cloud gives 95th-percentile deviation 8 μm, maximum 22 μm. Inlet volumetric flow waveform from Transonic TS410 pump sampled at 200 Hz with 1% RMS tracking error. Outlet pressure tuned to match measured mean pressure drop within 2%. All case/journal files version-controlled; key settings templated. Inlet turbulence intensity sensitivity tested. Stent positioning tolerances (±10 μm radial, ±2° rotation) propagated through sensitivity analysis.</t>
+          <t>Fluid density and viscosity measured with Anton Paar MCR 302 rheometer at 37°C; uncertainty ±0.5% (μ), ±0.2% (ρ). Inlet waveform from Transonic TS410 pump sensor at 200 Hz; 1% RMS tracking error. Geometry from 10 μm voxel micro-CT of as-deployed stent; segmented in Mimics 26.0 with 10 μm STL smoothing tolerance; metrology comparison shows 95th percentile surface deviation 8 μm, max 22 μm. Outlet BC tuned to match measured pressure drop. Inlet turbulence intensity 1% (sensitivity tested, non-impactful). Carreau–Yasuda parameters verified against published rheograms. All case inputs version-controlled with SHA-256 hashes.</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -3049,12 +3118,12 @@
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Experimental test article is representative of device geometry; phantom manufacturing quality documented</t>
+          <t>Phantom representative of intended device geometry; manufacturing quality documented; test article characterized</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>Single silicone phantom of representative 3.0 mm mildly curved coronary geometry (curvature radius 30 mm, 5% oversizing) manufactured and tested by independent FlowLab LLC. Phantom geometry verified against micro-CT scan used for CFD domain. Stent B deployed with as-built strut positions captured via micro-CT after deployment. No ensemble of multiple phantom specimens reported; single representative phantom used. Phantom represents mid-LAD anatomy but not patient-specific variation. No statistical characterization across multiple samples. Adequate for design-ranking and bench-comparison purpose given single-geometry COU.</t>
+          <t>Single silicone phantom of the deployed Pattern B stent geometry was used, manufactured by FlowLab LLC as an independent party. Phantom geometry is the same micro-CT-segmented geometry used for CFD. Refractive index of working fluid tuned to 1.413 for optical compatibility. Phantom produced to match 3.0 mm diameter, 30 mm radius of curvature, and 5% oversizing per deployment protocol. Only a single phantom was used (not a statistical population of specimens), which limits sample characterization. Production-representativeness confirmed via micro-CT; strut positions and recoil captured at 10 μm resolution.</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -3082,12 +3151,12 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Calibrated instrumentation; controlled environment; quantified measurement uncertainty; flow conditions well-characterized</t>
+          <t>Calibrated instrumentation; controlled and measured environment; measurement uncertainty quantified; flow conditions documented</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>TR-PIV acquired by independent FlowLab LLC at 500 fps with phase-locked acquisition to pump signal. Calibration plate with 10 μm dot spacing; calibration residuals &lt; 0.1 pixel. Refractive index matched to 1.413 to minimize wall reflections (residual glare &lt; 2% wall length, masked). Velocity uncertainty ±3% assessed via correlation peak ratio method. Near-wall shear proxy uncertainty 10–12% from least-squares fit in first 150 μm. Temperature controlled within ±0.5°C. Pressure drop measured with Validyne DP45 transducers. Pump trace recorded at 200 Hz (Transonic TS410). PIV data archived as HDF5 with ISA-Tab metadata manifest. Spatial resolution 32 μm per vector. Registration fiducial markers with RMS alignment error 35 μm.</t>
+          <t>PIV acquired by FlowLab LLC (independent lab) using Phantom VEO camera at 500 fps; calibration plate with 10 μm dot spacing, calibration residuals &lt; 0.1 pixel; spatial resolution 32 μm per vector. Velocity uncertainty ±3% assessed via correlation peak ratio method; near-wall shear proxy uncertainty ~10–12% (least-squares fit in first 150 μm). Pressure measured with Validyne DP45 differential transducer. Pump flow rate from Transonic TS410. Temperature controlled within ±0.5°C. Index matching with residual glare area &lt; 2% of wall length. Phase-locked acquisition with 40 bins over cardiac cycle. Data archived as HDF5 with ISA-Tab metadata manifest. All instrumentation calibrated and traceable.</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -3115,12 +3184,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>CFD boundary conditions demonstrably match experimental conditions; input parameter comparison documented; uncertainty propagated</t>
+          <t>CFD boundary conditions demonstrably matched to experimental conditions; input parameter comparison documented; measurement uncertainty propagated</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Inlet BC prescribed from the actual measured pump trace (Transonic TS410, 200 Hz sampling) with 1% RMS tracking error. Outlet pressure tuned to match measured mean pressure drop within 2%. Fluid properties match bench glycerol-water surrogate by construction (same fluid; measured properties used). Geometry derived from micro-CT of the same phantom used in PIV (surface deviation quantified to 8 μm 95th percentile). Temperature equivalency maintained within ±0.5°C in both CFD (isothermal 37°C) and experiment. Fiducial-based spatial registration with 35 μm RMS alignment error documented. Regions of low PIV confidence (&lt; 0.6) excluded from both datasets for fair comparison. Input uncertainty propagated through sensitivity analysis with RSS combination yielding ~8–10% total CFD uncertainty on TAWSS.</t>
+          <t>Inlet volumetric flow rate BC derived directly from same pump trace (Transonic TS410) used in PIV experiment; 1% RMS tracking error. Outlet static pressure tuned to reproduce measured mean pressure drop (within 2%). Fluid properties (density, viscosity) matched to measured bench fluid values. Phantom geometry identical between CFD (micro-CT segmentation) and PIV test article. Temperature matched to ±0.5°C. Registration of CFD wall coordinates to PIV plane via fiducial markers with 35 μm RMS alignment error. Inlet turbulence intensity set to 1% consistent with laminar regime; sensitivity confirmed non-impactful. All input matching documented with quantified deviations.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -3144,16 +3213,16 @@
         <v>3</v>
       </c>
       <c r="D15" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Pre-specified quantitative acceptance criteria; multiple comparison metrics; statistical validation; uncertainties included in comparison</t>
+          <t>Pre-specified quantitative metrics met; multiple comparison points; statistical validation metrics reported; uncertainty bands considered</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Pre-specified comparison targets defined at project kickoff and reviewed by device safety board. Multiple metrics reported: velocity nRMSE 7.1% (peak)/9.3% (mean) vs. targets ≤10%/≤12%; pressure drop 3.2% vs. target ≤7%; TAWSS Pearson r = 0.89 vs. target ≥0.85, median difference −6.4% vs. target &lt;15%, KS p = 0.21 vs. target &gt;0.1; OSI Pearson r = 0.86, median difference +4.9%, KS p = 0.18; hotspot co-location 93% within 0.2 mm. All targets met with margin. CFD uncertainty (~8–10%) and PIV uncertainty (3–12%) explicitly quantified and combined to confirm experiment–model discrepancies fall within combined uncertainty. Design-to-design differences (10–14% TAWSS reduction for B vs. A) confirmed to exceed summed uncertainties. Bias of −1.8% in velocity noted.</t>
+          <t>Pre-specified acceptance targets defined at project kickoff and reviewed by device safety board. Five comparison metrics evaluated: (1) Velocity nRMSE at 10 cross-sections: 7.1% peak (target ≤ 10%), 9.3% mean (target ≤ 12%) — Pass; (2) Pressure drop: CFD 3.2% above measured (target ≤ 7%) — Pass; (3) TAWSS map: Pearson r = 0.89 (target ≥ 0.85), median diff −6.4% (target &lt; 15%), KS p = 0.21 (target &gt; 0.1) — Pass; (4) OSI map: r = 0.86, median diff +4.9%, KS p = 0.18 — Pass; (5) Hotspot co-location: 93% of top-5% OSI regions within 0.2 mm. Combined simulation-side uncertainty ~8–10%; discrepancies fall within combined uncertainty. Design ranking differences (10–14% TAWSS reduction Pattern B vs. A) exceed summed uncertainties, confirming robust discrimination.</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3181,12 +3250,12 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>QoIs directly relate to neointimal hyperplasia risk; measurable both computationally and experimentally</t>
+          <t>QoIs directly address hemodynamic design concern; measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>TAWSS and OSI95 are established hemodynamic correlates of neointimal hyperplasia and stent thrombosis risk cited in the stent biomechanics literature (Augst et al. 2004 referenced). These QoIs are directly measurable from both CFD (area-integrated from wall face data) and PIV experiment (extrapolated near-wall velocity gradients). Area-averaged TAWSS, OSI spatial maps, and low-TAWSS area fraction (TAWSS &lt; 0.4 Pa) are computed consistently in both. The decision criterion (ranking of three patterns and acceptability of Pattern B) is directly operationalized through these QoIs. Velocity field and pressure drop serve as secondary validation QoIs confirming flow physics fidelity.</t>
+          <t>TAWSS and OSI95 are established hemodynamic correlates of neointimal hyperplasia and restenosis risk in coronary stenting, directly linking model outputs to the clinical design concern. Both QoIs are computable from CFD velocity/pressure fields and derivable from PIV near-wall velocity measurements, enabling direct experiment–model comparison. Pressure drop is an additional mechanistically relevant QoI for flow resistance. Hotspot localization (top 5% OSI regions) maps to anatomically specific risk zones. QoI selection justified by prior animal studies and literature cited in Section 1. Limitations of PIV-derived WSS (gradient extrapolation, ~10–12% uncertainty) acknowledged and reflected in acceptance thresholds.</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3210,16 +3279,16 @@
         <v>3</v>
       </c>
       <c r="D17" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation conditions match intended use geometry, flow regime, and fluid; gaps to in vivo deployment identified and bounded</t>
+          <t>Validation conditions match COU geometry, flow regime, and physics; gaps to full COU envelope documented</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>Validation performed in the same 3.0 mm phantom, same pulsatile flow regime (Re ≈ 350, Wo 1.6–2.3), same glycerol-water surrogate, and same stent geometry as the COU. Applicability bounds explicitly stated: strut width 70–90 μm, pitch ±15% of Pattern B, curvature radii 25–50 mm, mean flow 50–90 mL/min, HR 60–90 bpm. Known gaps documented: rigid phantom vs. in vivo compliance (bounded &lt; 5% effect), Newtonian surrogate vs. in vivo blood rheology (Carreau–Yasuda sensitivity: TAWSS −4.1% in wakes), patient-specific anatomy not represented, out-of-plane PIV limitation noted. A single representative phantom used rather than a range of anatomies. Validation directly supports the design-ranking and acceptability decision rather than a clinical endpoint claim.</t>
+          <t>Validation performed on the exact Pattern B geometry in the same phantom used for design assessment, under matched pulsatile flow conditions (Re ≈ 350, Womersley 1.6–2.3, flow rates 50–90 mL/min). Same fluid, temperature, and inlet waveform as design-decision simulations. Applicability bounds explicitly declared in Section 9: strut width 70–90 μm, pitch ±15% of Pattern B, curvature radii 25–50 mm, heart rate 60–90 bpm. Gaps documented: rigid phantom vs. compliant coronary wall (impact bounded &lt; 5%); PIV 2D plane vs. 3D secondary flows; Newtonian surrogate exact for bench but Carreau–Yasuda required for in vivo extension; no patient-specific calcification or eccentricity. Out-of-scope cases requiring separate analysis identified. Validation does not directly cover tight-bend geometries or microvascular coupling.</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3308,7 +3377,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>All pre-specified quantitative acceptance criteria for velocity field, pressure drop, TAWSS, and OSI comparisons between CFD and independent TR-PIV measurements were met with margin. Numerical uncertainties (GCI 3.8% for TAWSS on fine grid, mesh-induced OSI variation 4.5%) are small relative to design-to-design differences (10–14% TAWSS reduction Pattern B vs. A), supporting a robust and reliable design ranking. Input pedigree is well-characterized with quantified uncertainties. Key physical assumptions (laminar flow, rigid walls) are justified and their residual effects bounded. The model is accepted for the stated COU — ranking candidate coronary stent geometries and confirming Pattern B hemodynamic acceptability prior to tool-up — within the declared applicability limits (strut width 70–90 μm, curvature radius 25–50 mm, mean flow 50–90 mL/min, HR 60–90 bpm). Open items (rigid-wall FSI follow-on for highly compliant vessels, stereo-PIV for 3D secondary flows, micro-PIV for near-wall shear) are identified as future improvements and do not preclude acceptance at the current design phase given the moderate model risk level and the presence of parallel bench, animal, and clinical test gatekeepers.</t>
+          <t>All pre-specified acceptance targets for velocity field, pressure drop, TAWSS spatial distribution, and OSI spatial distribution were met with margin. Numerical uncertainties (GCI TAWSS 3.8% fine-grid, combined input/numerical uncertainty ~8–10%) are small relative to design-to-design differences (10–14% TAWSS reduction Pattern B vs. A), supporting robust design ranking. Independent PIV measurements by FlowLab LLC provide an anchored experimental comparator with quantified uncertainty. Physical model assumptions (laminar, rigid wall) are bounded and justified. Applicability limits are explicitly declared. Conditions: model is accepted for ranking of stent geometries with strut width 70–90 μm, pitch within ±15% of Pattern B, curvature radii 25–50 mm, and pulsatile flow within the declared envelope (50–90 mL/min, 60–90 bpm). Extension to tighter bends, fully compliant vessels, or patient-specific anatomy requires augmentation and additional validation.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -3318,7 +3387,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Fluids Group, CardioDesign R&amp;D (device safety board review of acceptance targets)</t>
+          <t>Fluids Group, CardioDesign R&amp;D; reviewed by device safety board</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
